--- a/excel-test-scenarios/testData/testFile.xlsx
+++ b/excel-test-scenarios/testData/testFile.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>sno</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>Green</t>
+  </si>
+  <si>
+    <t>Indian Mango</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -540,7 +543,7 @@
         <v>399</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
